--- a/تقييم المكتسبات - العرائش -08-10-2025.xlsx
+++ b/تقييم المكتسبات - العرائش -08-10-2025.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30006"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Administrator\OneDrive - OFPPT\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{2F808A4A-301E-436C-B96F-5DD7B3D539B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{6DE2081C-DAFB-40AB-B6EB-E5FB1B43FA4A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -18,12 +18,28 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">العرائش!#REF!</definedName>
   </definedNames>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191028"/>
+  <extLst>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+      <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2543" uniqueCount="757">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2563" uniqueCount="760">
   <si>
     <t>العملية</t>
   </si>
@@ -2294,13 +2310,22 @@
   </si>
   <si>
     <t>فرعية أولاد بوزيد</t>
+  </si>
+  <si>
+    <t>.</t>
+  </si>
+  <si>
+    <t>المديرية اللإقليمية</t>
+  </si>
+  <si>
+    <t>التفتيشية</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="4">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2346,7 +2371,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="7">
+  <borders count="8">
     <border>
       <left/>
       <right/>
@@ -2428,11 +2453,26 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -2472,6 +2512,9 @@
     </xf>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2863,27 +2906,27 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="B2:O369"/>
-  <sheetFormatPr defaultColWidth="11.44140625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="B2:O371"/>
+  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="14.45"/>
   <cols>
-    <col min="1" max="1" width="5.33203125" style="1" customWidth="1"/>
+    <col min="1" max="1" width="5.28515625" style="1" customWidth="1"/>
     <col min="2" max="2" width="23" style="1" customWidth="1"/>
-    <col min="3" max="4" width="27.88671875" style="1" customWidth="1"/>
-    <col min="5" max="5" width="14.6640625" style="1" customWidth="1"/>
-    <col min="6" max="6" width="33.109375" style="1" customWidth="1"/>
+    <col min="3" max="4" width="27.85546875" style="1" customWidth="1"/>
+    <col min="5" max="5" width="14.7109375" style="1" customWidth="1"/>
+    <col min="6" max="6" width="33.140625" style="1" customWidth="1"/>
     <col min="7" max="7" width="23" style="1" customWidth="1"/>
-    <col min="8" max="8" width="22.5546875" style="1" customWidth="1"/>
-    <col min="9" max="9" width="1.88671875" style="1" customWidth="1"/>
-    <col min="10" max="10" width="16.44140625" style="1" customWidth="1"/>
-    <col min="11" max="11" width="19.33203125" style="1" customWidth="1"/>
-    <col min="12" max="13" width="21.44140625" style="1" customWidth="1"/>
+    <col min="8" max="8" width="22.5703125" style="1" customWidth="1"/>
+    <col min="9" max="9" width="2.85546875" style="1" customWidth="1"/>
+    <col min="10" max="10" width="16.42578125" style="1" customWidth="1"/>
+    <col min="11" max="11" width="19.28515625" style="1" customWidth="1"/>
+    <col min="12" max="13" width="21.42578125" style="1" customWidth="1"/>
     <col min="14" max="14" width="26" style="1" customWidth="1"/>
-    <col min="15" max="15" width="22.44140625" style="1" customWidth="1"/>
-    <col min="16" max="16" width="11.44140625" style="1" customWidth="1"/>
-    <col min="17" max="16384" width="11.44140625" style="1"/>
+    <col min="15" max="15" width="22.42578125" style="1" customWidth="1"/>
+    <col min="16" max="16" width="11.42578125" style="1" customWidth="1"/>
+    <col min="17" max="16384" width="11.42578125" style="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:15" ht="21.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="2" spans="2:15" ht="21.75" customHeight="1">
       <c r="F2" s="9" t="s">
         <v>0</v>
       </c>
@@ -2899,11 +2942,11 @@
       <c r="N2" s="6"/>
       <c r="O2" s="6"/>
     </row>
-    <row r="3" spans="2:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="2:15" ht="15" customHeight="1">
       <c r="G3" s="5"/>
     </row>
-    <row r="4" spans="2:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="5" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="4" spans="2:15" ht="15.75" customHeight="1"/>
+    <row r="5" spans="2:15">
       <c r="B5" s="2" t="s">
         <v>2</v>
       </c>
@@ -2917,7 +2960,7 @@
         <v>45938</v>
       </c>
     </row>
-    <row r="8" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="8" spans="2:15">
       <c r="B8" s="8" t="s">
         <v>5</v>
       </c>
@@ -2952,7 +2995,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="9" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="9" spans="2:15">
       <c r="B9" s="1" t="s">
         <v>3</v>
       </c>
@@ -2984,7 +3027,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="10" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="10" spans="2:15">
       <c r="B10" s="1" t="s">
         <v>3</v>
       </c>
@@ -3016,7 +3059,7 @@
         <v>93.33</v>
       </c>
     </row>
-    <row r="11" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="11" spans="2:15">
       <c r="B11" s="1" t="s">
         <v>3</v>
       </c>
@@ -3048,7 +3091,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="12" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="12" spans="2:15">
       <c r="B12" s="1" t="s">
         <v>3</v>
       </c>
@@ -3080,7 +3123,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="13" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="13" spans="2:15">
       <c r="B13" s="1" t="s">
         <v>3</v>
       </c>
@@ -3112,7 +3155,7 @@
         <v>7.84</v>
       </c>
     </row>
-    <row r="14" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="14" spans="2:15">
       <c r="B14" s="1" t="s">
         <v>3</v>
       </c>
@@ -3144,7 +3187,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="15" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="15" spans="2:15">
       <c r="B15" s="1" t="s">
         <v>3</v>
       </c>
@@ -3176,7 +3219,7 @@
         <v>98.55</v>
       </c>
     </row>
-    <row r="16" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="16" spans="2:15">
       <c r="B16" s="1" t="s">
         <v>3</v>
       </c>
@@ -3208,7 +3251,7 @@
         <v>94.64</v>
       </c>
     </row>
-    <row r="17" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="17" spans="2:12">
       <c r="B17" s="1" t="s">
         <v>3</v>
       </c>
@@ -3240,7 +3283,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="18" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="18" spans="2:12">
       <c r="B18" s="1" t="s">
         <v>3</v>
       </c>
@@ -3272,7 +3315,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="19" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="19" spans="2:12">
       <c r="B19" s="1" t="s">
         <v>3</v>
       </c>
@@ -3304,7 +3347,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="20" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="20" spans="2:12">
       <c r="B20" s="1" t="s">
         <v>3</v>
       </c>
@@ -3336,7 +3379,7 @@
         <v>91.49</v>
       </c>
     </row>
-    <row r="21" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="21" spans="2:12">
       <c r="B21" s="1" t="s">
         <v>3</v>
       </c>
@@ -3368,7 +3411,7 @@
         <v>97.06</v>
       </c>
     </row>
-    <row r="22" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="22" spans="2:12">
       <c r="B22" s="1" t="s">
         <v>3</v>
       </c>
@@ -3400,7 +3443,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="23" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="23" spans="2:12">
       <c r="B23" s="1" t="s">
         <v>3</v>
       </c>
@@ -3432,7 +3475,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="24" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="24" spans="2:12">
       <c r="B24" s="1" t="s">
         <v>3</v>
       </c>
@@ -3464,7 +3507,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="25" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="25" spans="2:12">
       <c r="B25" s="1" t="s">
         <v>3</v>
       </c>
@@ -3496,7 +3539,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="26" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="26" spans="2:12">
       <c r="B26" s="1" t="s">
         <v>3</v>
       </c>
@@ -3528,7 +3571,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="27" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="27" spans="2:12">
       <c r="B27" s="1" t="s">
         <v>3</v>
       </c>
@@ -3560,7 +3603,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="28" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="28" spans="2:12">
       <c r="B28" s="1" t="s">
         <v>3</v>
       </c>
@@ -3592,7 +3635,7 @@
         <v>95.24</v>
       </c>
     </row>
-    <row r="29" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="29" spans="2:12">
       <c r="B29" s="1" t="s">
         <v>3</v>
       </c>
@@ -3624,7 +3667,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="30" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="30" spans="2:12">
       <c r="B30" s="1" t="s">
         <v>3</v>
       </c>
@@ -3656,7 +3699,7 @@
         <v>95.6</v>
       </c>
     </row>
-    <row r="31" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="31" spans="2:12">
       <c r="B31" s="1" t="s">
         <v>3</v>
       </c>
@@ -3688,7 +3731,7 @@
         <v>99.36</v>
       </c>
     </row>
-    <row r="32" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="32" spans="2:12">
       <c r="B32" s="1" t="s">
         <v>3</v>
       </c>
@@ -3720,7 +3763,7 @@
         <v>31.84</v>
       </c>
     </row>
-    <row r="33" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="33" spans="2:12">
       <c r="B33" s="1" t="s">
         <v>3</v>
       </c>
@@ -3752,7 +3795,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="34" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="34" spans="2:12">
       <c r="B34" s="1" t="s">
         <v>3</v>
       </c>
@@ -3784,7 +3827,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="35" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="35" spans="2:12">
       <c r="B35" s="1" t="s">
         <v>3</v>
       </c>
@@ -3816,7 +3859,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="36" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="36" spans="2:12">
       <c r="B36" s="1" t="s">
         <v>3</v>
       </c>
@@ -3848,7 +3891,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="37" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="37" spans="2:12">
       <c r="B37" s="1" t="s">
         <v>3</v>
       </c>
@@ -3880,7 +3923,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="38" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="38" spans="2:12">
       <c r="B38" s="1" t="s">
         <v>3</v>
       </c>
@@ -3912,7 +3955,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="39" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="39" spans="2:12">
       <c r="B39" s="1" t="s">
         <v>3</v>
       </c>
@@ -3944,7 +3987,7 @@
         <v>93.53</v>
       </c>
     </row>
-    <row r="40" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="40" spans="2:12">
       <c r="B40" s="1" t="s">
         <v>3</v>
       </c>
@@ -3976,7 +4019,7 @@
         <v>97.73</v>
       </c>
     </row>
-    <row r="41" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="41" spans="2:12">
       <c r="B41" s="1" t="s">
         <v>3</v>
       </c>
@@ -4008,7 +4051,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="42" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="42" spans="2:12">
       <c r="B42" s="1" t="s">
         <v>3</v>
       </c>
@@ -4040,7 +4083,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="43" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="43" spans="2:12">
       <c r="B43" s="1" t="s">
         <v>3</v>
       </c>
@@ -4072,7 +4115,7 @@
         <v>97.94</v>
       </c>
     </row>
-    <row r="44" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="44" spans="2:12">
       <c r="B44" s="1" t="s">
         <v>3</v>
       </c>
@@ -4104,7 +4147,7 @@
         <v>93.33</v>
       </c>
     </row>
-    <row r="45" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="45" spans="2:12">
       <c r="B45" s="1" t="s">
         <v>3</v>
       </c>
@@ -4136,7 +4179,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="46" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="46" spans="2:12">
       <c r="B46" s="1" t="s">
         <v>3</v>
       </c>
@@ -4168,7 +4211,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="47" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="47" spans="2:12">
       <c r="B47" s="1" t="s">
         <v>3</v>
       </c>
@@ -4200,7 +4243,7 @@
         <v>97.67</v>
       </c>
     </row>
-    <row r="48" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="48" spans="2:12">
       <c r="B48" s="1" t="s">
         <v>3</v>
       </c>
@@ -4232,7 +4275,7 @@
         <v>98.44</v>
       </c>
     </row>
-    <row r="49" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="49" spans="2:12">
       <c r="B49" s="1" t="s">
         <v>3</v>
       </c>
@@ -4264,7 +4307,7 @@
         <v>72.97</v>
       </c>
     </row>
-    <row r="50" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="50" spans="2:12">
       <c r="B50" s="1" t="s">
         <v>3</v>
       </c>
@@ -4296,7 +4339,7 @@
         <v>98.86</v>
       </c>
     </row>
-    <row r="51" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="51" spans="2:12">
       <c r="B51" s="1" t="s">
         <v>3</v>
       </c>
@@ -4328,7 +4371,7 @@
         <v>23.08</v>
       </c>
     </row>
-    <row r="52" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="52" spans="2:12">
       <c r="B52" s="1" t="s">
         <v>3</v>
       </c>
@@ -4360,7 +4403,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="53" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="53" spans="2:12">
       <c r="B53" s="1" t="s">
         <v>3</v>
       </c>
@@ -4392,7 +4435,7 @@
         <v>93.75</v>
       </c>
     </row>
-    <row r="54" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="54" spans="2:12">
       <c r="B54" s="1" t="s">
         <v>3</v>
       </c>
@@ -4424,7 +4467,7 @@
         <v>83.55</v>
       </c>
     </row>
-    <row r="55" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="55" spans="2:12">
       <c r="B55" s="1" t="s">
         <v>3</v>
       </c>
@@ -4456,7 +4499,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="56" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="56" spans="2:12">
       <c r="B56" s="1" t="s">
         <v>3</v>
       </c>
@@ -4488,7 +4531,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="57" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="57" spans="2:12">
       <c r="B57" s="1" t="s">
         <v>3</v>
       </c>
@@ -4520,7 +4563,7 @@
         <v>93.88</v>
       </c>
     </row>
-    <row r="58" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="58" spans="2:12">
       <c r="B58" s="1" t="s">
         <v>3</v>
       </c>
@@ -4552,7 +4595,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="59" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="59" spans="2:12">
       <c r="B59" s="1" t="s">
         <v>3</v>
       </c>
@@ -4584,7 +4627,7 @@
         <v>98.5</v>
       </c>
     </row>
-    <row r="60" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="60" spans="2:12">
       <c r="B60" s="1" t="s">
         <v>3</v>
       </c>
@@ -4616,7 +4659,7 @@
         <v>94.29</v>
       </c>
     </row>
-    <row r="61" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="61" spans="2:12">
       <c r="B61" s="1" t="s">
         <v>3</v>
       </c>
@@ -4648,7 +4691,7 @@
         <v>98.8</v>
       </c>
     </row>
-    <row r="62" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="62" spans="2:12">
       <c r="B62" s="1" t="s">
         <v>3</v>
       </c>
@@ -4680,7 +4723,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="63" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="63" spans="2:12">
       <c r="B63" s="1" t="s">
         <v>3</v>
       </c>
@@ -4712,7 +4755,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="64" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="64" spans="2:12">
       <c r="B64" s="1" t="s">
         <v>3</v>
       </c>
@@ -4744,7 +4787,7 @@
         <v>91.55</v>
       </c>
     </row>
-    <row r="65" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="65" spans="2:12">
       <c r="B65" s="1" t="s">
         <v>3</v>
       </c>
@@ -4776,7 +4819,7 @@
         <v>97.1</v>
       </c>
     </row>
-    <row r="66" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="66" spans="2:12">
       <c r="B66" s="1" t="s">
         <v>3</v>
       </c>
@@ -4808,7 +4851,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="67" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="67" spans="2:12">
       <c r="B67" s="1" t="s">
         <v>3</v>
       </c>
@@ -4840,7 +4883,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="68" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="68" spans="2:12">
       <c r="B68" s="1" t="s">
         <v>3</v>
       </c>
@@ -4872,7 +4915,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="69" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="69" spans="2:12">
       <c r="B69" s="1" t="s">
         <v>3</v>
       </c>
@@ -4904,7 +4947,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="70" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="70" spans="2:12">
       <c r="B70" s="1" t="s">
         <v>3</v>
       </c>
@@ -4936,7 +4979,7 @@
         <v>90.91</v>
       </c>
     </row>
-    <row r="71" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="71" spans="2:12">
       <c r="B71" s="1" t="s">
         <v>3</v>
       </c>
@@ -4968,7 +5011,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="72" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="72" spans="2:12">
       <c r="B72" s="1" t="s">
         <v>3</v>
       </c>
@@ -5000,7 +5043,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="73" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="73" spans="2:12">
       <c r="B73" s="1" t="s">
         <v>3</v>
       </c>
@@ -5032,7 +5075,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="74" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="74" spans="2:12">
       <c r="B74" s="1" t="s">
         <v>3</v>
       </c>
@@ -5064,7 +5107,7 @@
         <v>8.33</v>
       </c>
     </row>
-    <row r="75" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="75" spans="2:12">
       <c r="B75" s="1" t="s">
         <v>3</v>
       </c>
@@ -5096,7 +5139,7 @@
         <v>6.25</v>
       </c>
     </row>
-    <row r="76" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="76" spans="2:12">
       <c r="B76" s="1" t="s">
         <v>3</v>
       </c>
@@ -5128,7 +5171,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="77" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="77" spans="2:12">
       <c r="B77" s="1" t="s">
         <v>3</v>
       </c>
@@ -5160,7 +5203,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="78" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="78" spans="2:12">
       <c r="B78" s="1" t="s">
         <v>3</v>
       </c>
@@ -5192,7 +5235,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="79" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="79" spans="2:12">
       <c r="B79" s="1" t="s">
         <v>3</v>
       </c>
@@ -5224,7 +5267,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="80" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="80" spans="2:12">
       <c r="B80" s="1" t="s">
         <v>3</v>
       </c>
@@ -5256,7 +5299,7 @@
         <v>37.5</v>
       </c>
     </row>
-    <row r="81" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="81" spans="2:12">
       <c r="B81" s="1" t="s">
         <v>3</v>
       </c>
@@ -5288,7 +5331,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="82" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="82" spans="2:12">
       <c r="B82" s="1" t="s">
         <v>3</v>
       </c>
@@ -5320,7 +5363,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="83" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="83" spans="2:12">
       <c r="B83" s="1" t="s">
         <v>3</v>
       </c>
@@ -5352,7 +5395,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="84" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="84" spans="2:12">
       <c r="B84" s="1" t="s">
         <v>3</v>
       </c>
@@ -5384,7 +5427,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="85" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="85" spans="2:12">
       <c r="B85" s="1" t="s">
         <v>3</v>
       </c>
@@ -5416,7 +5459,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="86" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="86" spans="2:12">
       <c r="B86" s="1" t="s">
         <v>3</v>
       </c>
@@ -5448,7 +5491,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="87" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="87" spans="2:12">
       <c r="B87" s="1" t="s">
         <v>3</v>
       </c>
@@ -5480,7 +5523,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="88" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="88" spans="2:12">
       <c r="B88" s="1" t="s">
         <v>3</v>
       </c>
@@ -5512,7 +5555,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="89" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="89" spans="2:12">
       <c r="B89" s="1" t="s">
         <v>3</v>
       </c>
@@ -5544,7 +5587,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="90" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="90" spans="2:12">
       <c r="B90" s="1" t="s">
         <v>3</v>
       </c>
@@ -5576,7 +5619,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="91" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="91" spans="2:12">
       <c r="B91" s="1" t="s">
         <v>3</v>
       </c>
@@ -5608,7 +5651,7 @@
         <v>98.23</v>
       </c>
     </row>
-    <row r="92" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="92" spans="2:12">
       <c r="B92" s="1" t="s">
         <v>3</v>
       </c>
@@ -5640,7 +5683,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="93" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="93" spans="2:12">
       <c r="B93" s="1" t="s">
         <v>3</v>
       </c>
@@ -5672,7 +5715,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="94" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="94" spans="2:12">
       <c r="B94" s="1" t="s">
         <v>3</v>
       </c>
@@ -5704,7 +5747,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="95" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="95" spans="2:12">
       <c r="B95" s="1" t="s">
         <v>3</v>
       </c>
@@ -5736,7 +5779,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="96" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="96" spans="2:12">
       <c r="B96" s="1" t="s">
         <v>3</v>
       </c>
@@ -5768,7 +5811,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="97" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="97" spans="2:12">
       <c r="B97" s="1" t="s">
         <v>3</v>
       </c>
@@ -5800,7 +5843,7 @@
         <v>15.38</v>
       </c>
     </row>
-    <row r="98" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="98" spans="2:12">
       <c r="B98" s="1" t="s">
         <v>3</v>
       </c>
@@ -5832,7 +5875,7 @@
         <v>94.44</v>
       </c>
     </row>
-    <row r="99" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="99" spans="2:12">
       <c r="B99" s="1" t="s">
         <v>3</v>
       </c>
@@ -5864,7 +5907,7 @@
         <v>11.36</v>
       </c>
     </row>
-    <row r="100" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="100" spans="2:12">
       <c r="B100" s="1" t="s">
         <v>3</v>
       </c>
@@ -5896,7 +5939,7 @@
         <v>97.87</v>
       </c>
     </row>
-    <row r="101" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="101" spans="2:12">
       <c r="B101" s="1" t="s">
         <v>3</v>
       </c>
@@ -5928,7 +5971,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="102" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="102" spans="2:12">
       <c r="B102" s="1" t="s">
         <v>3</v>
       </c>
@@ -5960,7 +6003,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="103" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="103" spans="2:12">
       <c r="B103" s="1" t="s">
         <v>3</v>
       </c>
@@ -5992,7 +6035,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="104" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="104" spans="2:12">
       <c r="B104" s="1" t="s">
         <v>3</v>
       </c>
@@ -6024,7 +6067,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="105" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="105" spans="2:12">
       <c r="B105" s="1" t="s">
         <v>3</v>
       </c>
@@ -6056,7 +6099,7 @@
         <v>96.99</v>
       </c>
     </row>
-    <row r="106" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="106" spans="2:12">
       <c r="B106" s="1" t="s">
         <v>3</v>
       </c>
@@ -6088,7 +6131,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="107" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="107" spans="2:12">
       <c r="B107" s="1" t="s">
         <v>3</v>
       </c>
@@ -6120,7 +6163,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="108" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="108" spans="2:12">
       <c r="B108" s="1" t="s">
         <v>3</v>
       </c>
@@ -6152,7 +6195,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="109" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="109" spans="2:12">
       <c r="B109" s="1" t="s">
         <v>3</v>
       </c>
@@ -6184,7 +6227,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="110" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="110" spans="2:12">
       <c r="B110" s="1" t="s">
         <v>3</v>
       </c>
@@ -6216,7 +6259,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="111" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="111" spans="2:12">
       <c r="B111" s="1" t="s">
         <v>3</v>
       </c>
@@ -6248,7 +6291,7 @@
         <v>90.2</v>
       </c>
     </row>
-    <row r="112" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="112" spans="2:12">
       <c r="B112" s="1" t="s">
         <v>3</v>
       </c>
@@ -6280,7 +6323,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="113" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="113" spans="2:12">
       <c r="B113" s="1" t="s">
         <v>3</v>
       </c>
@@ -6312,7 +6355,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="114" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="114" spans="2:12">
       <c r="B114" s="1" t="s">
         <v>3</v>
       </c>
@@ -6344,7 +6387,7 @@
         <v>96.15</v>
       </c>
     </row>
-    <row r="115" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="115" spans="2:12">
       <c r="B115" s="1" t="s">
         <v>3</v>
       </c>
@@ -6376,7 +6419,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="116" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="116" spans="2:12">
       <c r="B116" s="1" t="s">
         <v>3</v>
       </c>
@@ -6408,7 +6451,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="117" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="117" spans="2:12">
       <c r="B117" s="1" t="s">
         <v>3</v>
       </c>
@@ -6440,7 +6483,7 @@
         <v>96.2</v>
       </c>
     </row>
-    <row r="118" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="118" spans="2:12">
       <c r="B118" s="1" t="s">
         <v>3</v>
       </c>
@@ -6472,7 +6515,7 @@
         <v>80.31</v>
       </c>
     </row>
-    <row r="119" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="119" spans="2:12">
       <c r="B119" s="1" t="s">
         <v>3</v>
       </c>
@@ -6504,7 +6547,7 @@
         <v>93.18</v>
       </c>
     </row>
-    <row r="120" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="120" spans="2:12">
       <c r="B120" s="1" t="s">
         <v>3</v>
       </c>
@@ -6536,7 +6579,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="121" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="121" spans="2:12">
       <c r="B121" s="1" t="s">
         <v>3</v>
       </c>
@@ -6568,7 +6611,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="122" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="122" spans="2:12">
       <c r="B122" s="1" t="s">
         <v>3</v>
       </c>
@@ -6600,7 +6643,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="123" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="123" spans="2:12">
       <c r="B123" s="1" t="s">
         <v>3</v>
       </c>
@@ -6632,7 +6675,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="124" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="124" spans="2:12">
       <c r="B124" s="1" t="s">
         <v>3</v>
       </c>
@@ -6664,7 +6707,7 @@
         <v>16.670000000000002</v>
       </c>
     </row>
-    <row r="125" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="125" spans="2:12">
       <c r="B125" s="1" t="s">
         <v>3</v>
       </c>
@@ -6696,7 +6739,7 @@
         <v>51.56</v>
       </c>
     </row>
-    <row r="126" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="126" spans="2:12">
       <c r="B126" s="1" t="s">
         <v>3</v>
       </c>
@@ -6728,7 +6771,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="127" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="127" spans="2:12">
       <c r="B127" s="1" t="s">
         <v>3</v>
       </c>
@@ -6760,7 +6803,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="128" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="128" spans="2:12">
       <c r="B128" s="1" t="s">
         <v>3</v>
       </c>
@@ -6792,7 +6835,7 @@
         <v>87.5</v>
       </c>
     </row>
-    <row r="129" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="129" spans="2:12">
       <c r="B129" s="1" t="s">
         <v>3</v>
       </c>
@@ -6824,7 +6867,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="130" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="130" spans="2:12">
       <c r="B130" s="1" t="s">
         <v>3</v>
       </c>
@@ -6856,7 +6899,7 @@
         <v>22.22</v>
       </c>
     </row>
-    <row r="131" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="131" spans="2:12">
       <c r="B131" s="1" t="s">
         <v>3</v>
       </c>
@@ -6888,7 +6931,7 @@
         <v>6.25</v>
       </c>
     </row>
-    <row r="132" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="132" spans="2:12">
       <c r="B132" s="1" t="s">
         <v>3</v>
       </c>
@@ -6920,7 +6963,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="133" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="133" spans="2:12">
       <c r="B133" s="1" t="s">
         <v>3</v>
       </c>
@@ -6952,7 +6995,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="134" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="134" spans="2:12">
       <c r="B134" s="1" t="s">
         <v>3</v>
       </c>
@@ -6984,7 +7027,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="135" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="135" spans="2:12">
       <c r="B135" s="1" t="s">
         <v>3</v>
       </c>
@@ -7016,7 +7059,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="136" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="136" spans="2:12">
       <c r="B136" s="1" t="s">
         <v>3</v>
       </c>
@@ -7048,7 +7091,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="137" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="137" spans="2:12">
       <c r="B137" s="1" t="s">
         <v>3</v>
       </c>
@@ -7080,7 +7123,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="138" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="138" spans="2:12">
       <c r="B138" s="1" t="s">
         <v>3</v>
       </c>
@@ -7112,7 +7155,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="139" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="139" spans="2:12">
       <c r="B139" s="1" t="s">
         <v>3</v>
       </c>
@@ -7144,7 +7187,7 @@
         <v>85.71</v>
       </c>
     </row>
-    <row r="140" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="140" spans="2:12">
       <c r="B140" s="1" t="s">
         <v>3</v>
       </c>
@@ -7176,7 +7219,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="141" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="141" spans="2:12">
       <c r="B141" s="1" t="s">
         <v>3</v>
       </c>
@@ -7208,7 +7251,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="142" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="142" spans="2:12">
       <c r="B142" s="1" t="s">
         <v>3</v>
       </c>
@@ -7240,7 +7283,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="143" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="143" spans="2:12">
       <c r="B143" s="1" t="s">
         <v>3</v>
       </c>
@@ -7272,7 +7315,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="144" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="144" spans="2:12">
       <c r="B144" s="1" t="s">
         <v>3</v>
       </c>
@@ -7304,7 +7347,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="145" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="145" spans="2:12">
       <c r="B145" s="1" t="s">
         <v>3</v>
       </c>
@@ -7336,7 +7379,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="146" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="146" spans="2:12">
       <c r="B146" s="1" t="s">
         <v>3</v>
       </c>
@@ -7368,7 +7411,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="147" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="147" spans="2:12">
       <c r="B147" s="1" t="s">
         <v>3</v>
       </c>
@@ -7400,7 +7443,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="148" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="148" spans="2:12">
       <c r="B148" s="1" t="s">
         <v>3</v>
       </c>
@@ -7432,7 +7475,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="149" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="149" spans="2:12">
       <c r="B149" s="1" t="s">
         <v>3</v>
       </c>
@@ -7464,7 +7507,7 @@
         <v>88.89</v>
       </c>
     </row>
-    <row r="150" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="150" spans="2:12">
       <c r="B150" s="1" t="s">
         <v>3</v>
       </c>
@@ -7496,7 +7539,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="151" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="151" spans="2:12">
       <c r="B151" s="1" t="s">
         <v>3</v>
       </c>
@@ -7528,7 +7571,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="152" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="152" spans="2:12">
       <c r="B152" s="1" t="s">
         <v>3</v>
       </c>
@@ -7560,7 +7603,7 @@
         <v>66.67</v>
       </c>
     </row>
-    <row r="153" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="153" spans="2:12">
       <c r="B153" s="1" t="s">
         <v>3</v>
       </c>
@@ -7592,7 +7635,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="154" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="154" spans="2:12">
       <c r="B154" s="1" t="s">
         <v>3</v>
       </c>
@@ -7624,7 +7667,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="155" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="155" spans="2:12">
       <c r="B155" s="1" t="s">
         <v>3</v>
       </c>
@@ -7656,7 +7699,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="156" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="156" spans="2:12">
       <c r="B156" s="1" t="s">
         <v>3</v>
       </c>
@@ -7688,7 +7731,7 @@
         <v>87.5</v>
       </c>
     </row>
-    <row r="157" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="157" spans="2:12">
       <c r="B157" s="1" t="s">
         <v>3</v>
       </c>
@@ -7720,7 +7763,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="158" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="158" spans="2:12">
       <c r="B158" s="1" t="s">
         <v>3</v>
       </c>
@@ -7752,7 +7795,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="159" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="159" spans="2:12">
       <c r="B159" s="1" t="s">
         <v>3</v>
       </c>
@@ -7784,7 +7827,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="160" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="160" spans="2:12">
       <c r="B160" s="1" t="s">
         <v>3</v>
       </c>
@@ -7816,7 +7859,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="161" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="161" spans="2:12">
       <c r="B161" s="1" t="s">
         <v>3</v>
       </c>
@@ -7848,7 +7891,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="162" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="162" spans="2:12">
       <c r="B162" s="1" t="s">
         <v>3</v>
       </c>
@@ -7880,7 +7923,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="163" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="163" spans="2:12">
       <c r="B163" s="1" t="s">
         <v>3</v>
       </c>
@@ -7912,7 +7955,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="164" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="164" spans="2:12">
       <c r="B164" s="1" t="s">
         <v>3</v>
       </c>
@@ -7944,7 +7987,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="165" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="165" spans="2:12">
       <c r="B165" s="1" t="s">
         <v>3</v>
       </c>
@@ -7976,7 +8019,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="166" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="166" spans="2:12">
       <c r="B166" s="1" t="s">
         <v>3</v>
       </c>
@@ -8008,7 +8051,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="167" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="167" spans="2:12">
       <c r="B167" s="1" t="s">
         <v>3</v>
       </c>
@@ -8040,7 +8083,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="168" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="168" spans="2:12">
       <c r="B168" s="1" t="s">
         <v>3</v>
       </c>
@@ -8072,7 +8115,7 @@
         <v>97.06</v>
       </c>
     </row>
-    <row r="169" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="169" spans="2:12">
       <c r="B169" s="1" t="s">
         <v>3</v>
       </c>
@@ -8104,7 +8147,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="170" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="170" spans="2:12">
       <c r="B170" s="1" t="s">
         <v>3</v>
       </c>
@@ -8136,7 +8179,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="171" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="171" spans="2:12">
       <c r="B171" s="1" t="s">
         <v>3</v>
       </c>
@@ -8168,7 +8211,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="172" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="172" spans="2:12">
       <c r="B172" s="1" t="s">
         <v>3</v>
       </c>
@@ -8200,7 +8243,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="173" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="173" spans="2:12">
       <c r="B173" s="1" t="s">
         <v>3</v>
       </c>
@@ -8232,7 +8275,7 @@
         <v>95.45</v>
       </c>
     </row>
-    <row r="174" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="174" spans="2:12">
       <c r="B174" s="1" t="s">
         <v>3</v>
       </c>
@@ -8264,7 +8307,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="175" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="175" spans="2:12">
       <c r="B175" s="1" t="s">
         <v>3</v>
       </c>
@@ -8296,7 +8339,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="176" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="176" spans="2:12">
       <c r="B176" s="1" t="s">
         <v>3</v>
       </c>
@@ -8328,7 +8371,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="177" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="177" spans="2:12">
       <c r="B177" s="1" t="s">
         <v>3</v>
       </c>
@@ -8360,7 +8403,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="178" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="178" spans="2:12">
       <c r="B178" s="1" t="s">
         <v>3</v>
       </c>
@@ -8392,7 +8435,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="179" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="179" spans="2:12">
       <c r="B179" s="1" t="s">
         <v>3</v>
       </c>
@@ -8424,7 +8467,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="180" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="180" spans="2:12">
       <c r="B180" s="1" t="s">
         <v>3</v>
       </c>
@@ -8456,7 +8499,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="181" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="181" spans="2:12">
       <c r="B181" s="1" t="s">
         <v>3</v>
       </c>
@@ -8488,7 +8531,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="182" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="182" spans="2:12">
       <c r="B182" s="1" t="s">
         <v>3</v>
       </c>
@@ -8520,7 +8563,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="183" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="183" spans="2:12">
       <c r="B183" s="1" t="s">
         <v>3</v>
       </c>
@@ -8552,7 +8595,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="184" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="184" spans="2:12">
       <c r="B184" s="1" t="s">
         <v>3</v>
       </c>
@@ -8584,7 +8627,7 @@
         <v>90.48</v>
       </c>
     </row>
-    <row r="185" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="185" spans="2:12">
       <c r="B185" s="1" t="s">
         <v>3</v>
       </c>
@@ -8616,7 +8659,7 @@
         <v>96.97</v>
       </c>
     </row>
-    <row r="186" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="186" spans="2:12">
       <c r="B186" s="1" t="s">
         <v>3</v>
       </c>
@@ -8648,7 +8691,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="187" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="187" spans="2:12">
       <c r="B187" s="1" t="s">
         <v>3</v>
       </c>
@@ -8680,7 +8723,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="188" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="188" spans="2:12">
       <c r="B188" s="1" t="s">
         <v>3</v>
       </c>
@@ -8712,7 +8755,7 @@
         <v>28.57</v>
       </c>
     </row>
-    <row r="189" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="189" spans="2:12">
       <c r="B189" s="1" t="s">
         <v>3</v>
       </c>
@@ -8744,7 +8787,7 @@
         <v>17.39</v>
       </c>
     </row>
-    <row r="190" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="190" spans="2:12">
       <c r="B190" s="1" t="s">
         <v>3</v>
       </c>
@@ -8776,7 +8819,7 @@
         <v>95.05</v>
       </c>
     </row>
-    <row r="191" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="191" spans="2:12">
       <c r="B191" s="1" t="s">
         <v>3</v>
       </c>
@@ -8808,7 +8851,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="192" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="192" spans="2:12">
       <c r="B192" s="1" t="s">
         <v>3</v>
       </c>
@@ -8840,7 +8883,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="193" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="193" spans="2:12">
       <c r="B193" s="1" t="s">
         <v>3</v>
       </c>
@@ -8872,7 +8915,7 @@
         <v>97.06</v>
       </c>
     </row>
-    <row r="194" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="194" spans="2:12">
       <c r="B194" s="1" t="s">
         <v>3</v>
       </c>
@@ -8904,7 +8947,7 @@
         <v>97.44</v>
       </c>
     </row>
-    <row r="195" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="195" spans="2:12">
       <c r="B195" s="1" t="s">
         <v>3</v>
       </c>
@@ -8936,7 +8979,7 @@
         <v>96.88</v>
       </c>
     </row>
-    <row r="196" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="196" spans="2:12">
       <c r="B196" s="1" t="s">
         <v>3</v>
       </c>
@@ -8968,7 +9011,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="197" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="197" spans="2:12">
       <c r="B197" s="1" t="s">
         <v>3</v>
       </c>
@@ -9000,7 +9043,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="198" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="198" spans="2:12">
       <c r="B198" s="1" t="s">
         <v>3</v>
       </c>
@@ -9032,7 +9075,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="199" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="199" spans="2:12">
       <c r="B199" s="1" t="s">
         <v>3</v>
       </c>
@@ -9064,7 +9107,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="200" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="200" spans="2:12">
       <c r="B200" s="1" t="s">
         <v>3</v>
       </c>
@@ -9096,7 +9139,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="201" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="201" spans="2:12">
       <c r="B201" s="1" t="s">
         <v>3</v>
       </c>
@@ -9128,7 +9171,7 @@
         <v>97.06</v>
       </c>
     </row>
-    <row r="202" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="202" spans="2:12">
       <c r="B202" s="1" t="s">
         <v>3</v>
       </c>
@@ -9160,7 +9203,7 @@
         <v>23.08</v>
       </c>
     </row>
-    <row r="203" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="203" spans="2:12">
       <c r="B203" s="1" t="s">
         <v>3</v>
       </c>
@@ -9192,7 +9235,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="204" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="204" spans="2:12">
       <c r="B204" s="1" t="s">
         <v>3</v>
       </c>
@@ -9224,7 +9267,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="205" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="205" spans="2:12">
       <c r="B205" s="1" t="s">
         <v>3</v>
       </c>
@@ -9256,7 +9299,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="206" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="206" spans="2:12">
       <c r="B206" s="1" t="s">
         <v>3</v>
       </c>
@@ -9288,7 +9331,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="207" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="207" spans="2:12">
       <c r="B207" s="1" t="s">
         <v>3</v>
       </c>
@@ -9320,7 +9363,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="208" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="208" spans="2:12">
       <c r="B208" s="1" t="s">
         <v>3</v>
       </c>
@@ -9352,7 +9395,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="209" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="209" spans="2:12">
       <c r="B209" s="1" t="s">
         <v>3</v>
       </c>
@@ -9384,7 +9427,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="210" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="210" spans="2:12">
       <c r="B210" s="1" t="s">
         <v>3</v>
       </c>
@@ -9416,7 +9459,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="211" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="211" spans="2:12">
       <c r="B211" s="1" t="s">
         <v>3</v>
       </c>
@@ -9448,7 +9491,7 @@
         <v>98.36</v>
       </c>
     </row>
-    <row r="212" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="212" spans="2:12">
       <c r="B212" s="1" t="s">
         <v>3</v>
       </c>
@@ -9480,7 +9523,7 @@
         <v>96.23</v>
       </c>
     </row>
-    <row r="213" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="213" spans="2:12">
       <c r="B213" s="1" t="s">
         <v>3</v>
       </c>
@@ -9512,7 +9555,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="214" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="214" spans="2:12">
       <c r="B214" s="1" t="s">
         <v>3</v>
       </c>
@@ -9544,7 +9587,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="215" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="215" spans="2:12">
       <c r="B215" s="1" t="s">
         <v>3</v>
       </c>
@@ -9576,7 +9619,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="216" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="216" spans="2:12">
       <c r="B216" s="1" t="s">
         <v>3</v>
       </c>
@@ -9608,7 +9651,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="217" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="217" spans="2:12">
       <c r="B217" s="1" t="s">
         <v>3</v>
       </c>
@@ -9640,7 +9683,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="218" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="218" spans="2:12">
       <c r="B218" s="1" t="s">
         <v>3</v>
       </c>
@@ -9672,7 +9715,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="219" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="219" spans="2:12">
       <c r="B219" s="1" t="s">
         <v>3</v>
       </c>
@@ -9704,7 +9747,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="220" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="220" spans="2:12">
       <c r="B220" s="1" t="s">
         <v>3</v>
       </c>
@@ -9736,7 +9779,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="221" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="221" spans="2:12">
       <c r="B221" s="1" t="s">
         <v>3</v>
       </c>
@@ -9768,7 +9811,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="222" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="222" spans="2:12">
       <c r="B222" s="1" t="s">
         <v>3</v>
       </c>
@@ -9800,7 +9843,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="223" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="223" spans="2:12">
       <c r="B223" s="1" t="s">
         <v>3</v>
       </c>
@@ -9832,7 +9875,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="224" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="224" spans="2:12">
       <c r="B224" s="1" t="s">
         <v>3</v>
       </c>
@@ -9864,7 +9907,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="225" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="225" spans="2:12">
       <c r="B225" s="1" t="s">
         <v>3</v>
       </c>
@@ -9896,7 +9939,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="226" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="226" spans="2:12">
       <c r="B226" s="1" t="s">
         <v>3</v>
       </c>
@@ -9928,7 +9971,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="227" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="227" spans="2:12">
       <c r="B227" s="1" t="s">
         <v>3</v>
       </c>
@@ -9960,7 +10003,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="228" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="228" spans="2:12">
       <c r="B228" s="1" t="s">
         <v>3</v>
       </c>
@@ -9992,7 +10035,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="229" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="229" spans="2:12">
       <c r="B229" s="1" t="s">
         <v>3</v>
       </c>
@@ -10024,7 +10067,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="230" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="230" spans="2:12">
       <c r="B230" s="1" t="s">
         <v>3</v>
       </c>
@@ -10056,7 +10099,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="231" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="231" spans="2:12">
       <c r="B231" s="1" t="s">
         <v>3</v>
       </c>
@@ -10088,7 +10131,7 @@
         <v>95.24</v>
       </c>
     </row>
-    <row r="232" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="232" spans="2:12">
       <c r="B232" s="1" t="s">
         <v>3</v>
       </c>
@@ -10120,7 +10163,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="233" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="233" spans="2:12">
       <c r="B233" s="1" t="s">
         <v>3</v>
       </c>
@@ -10152,7 +10195,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="234" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="234" spans="2:12">
       <c r="B234" s="1" t="s">
         <v>3</v>
       </c>
@@ -10184,7 +10227,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="235" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="235" spans="2:12">
       <c r="B235" s="1" t="s">
         <v>3</v>
       </c>
@@ -10216,7 +10259,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="236" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="236" spans="2:12">
       <c r="B236" s="1" t="s">
         <v>3</v>
       </c>
@@ -10248,7 +10291,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="237" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="237" spans="2:12">
       <c r="B237" s="1" t="s">
         <v>3</v>
       </c>
@@ -10280,7 +10323,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="238" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="238" spans="2:12">
       <c r="B238" s="1" t="s">
         <v>3</v>
       </c>
@@ -10312,7 +10355,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="239" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="239" spans="2:12">
       <c r="B239" s="1" t="s">
         <v>3</v>
       </c>
@@ -10344,7 +10387,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="240" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="240" spans="2:12">
       <c r="B240" s="1" t="s">
         <v>3</v>
       </c>
@@ -10376,7 +10419,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="241" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="241" spans="2:12">
       <c r="B241" s="1" t="s">
         <v>3</v>
       </c>
@@ -10408,7 +10451,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="242" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="242" spans="2:12">
       <c r="B242" s="1" t="s">
         <v>3</v>
       </c>
@@ -10440,7 +10483,7 @@
         <v>91.67</v>
       </c>
     </row>
-    <row r="243" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="243" spans="2:12">
       <c r="B243" s="1" t="s">
         <v>3</v>
       </c>
@@ -10472,7 +10515,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="244" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="244" spans="2:12">
       <c r="B244" s="1" t="s">
         <v>3</v>
       </c>
@@ -10504,7 +10547,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="245" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="245" spans="2:12">
       <c r="B245" s="1" t="s">
         <v>3</v>
       </c>
@@ -10536,7 +10579,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="246" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="246" spans="2:12">
       <c r="B246" s="1" t="s">
         <v>3</v>
       </c>
@@ -10568,7 +10611,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="247" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="247" spans="2:12">
       <c r="B247" s="1" t="s">
         <v>3</v>
       </c>
@@ -10600,7 +10643,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="248" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="248" spans="2:12">
       <c r="B248" s="1" t="s">
         <v>3</v>
       </c>
@@ -10632,7 +10675,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="249" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="249" spans="2:12">
       <c r="B249" s="1" t="s">
         <v>3</v>
       </c>
@@ -10664,7 +10707,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="250" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="250" spans="2:12">
       <c r="B250" s="1" t="s">
         <v>3</v>
       </c>
@@ -10696,7 +10739,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="251" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="251" spans="2:12">
       <c r="B251" s="1" t="s">
         <v>3</v>
       </c>
@@ -10728,7 +10771,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="252" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="252" spans="2:12">
       <c r="B252" s="1" t="s">
         <v>3</v>
       </c>
@@ -10760,7 +10803,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="253" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="253" spans="2:12">
       <c r="B253" s="1" t="s">
         <v>3</v>
       </c>
@@ -10792,7 +10835,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="254" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="254" spans="2:12">
       <c r="B254" s="1" t="s">
         <v>3</v>
       </c>
@@ -10824,7 +10867,7 @@
         <v>66.67</v>
       </c>
     </row>
-    <row r="255" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="255" spans="2:12">
       <c r="B255" s="1" t="s">
         <v>3</v>
       </c>
@@ -10856,7 +10899,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="256" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="256" spans="2:12">
       <c r="B256" s="1" t="s">
         <v>3</v>
       </c>
@@ -10888,7 +10931,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="257" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="257" spans="2:12">
       <c r="B257" s="1" t="s">
         <v>3</v>
       </c>
@@ -10920,7 +10963,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="258" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="258" spans="2:12">
       <c r="B258" s="1" t="s">
         <v>3</v>
       </c>
@@ -10952,7 +10995,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="259" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="259" spans="2:12">
       <c r="B259" s="1" t="s">
         <v>3</v>
       </c>
@@ -10984,7 +11027,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="260" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="260" spans="2:12">
       <c r="B260" s="1" t="s">
         <v>3</v>
       </c>
@@ -11016,7 +11059,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="261" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="261" spans="2:12">
       <c r="B261" s="1" t="s">
         <v>3</v>
       </c>
@@ -11048,7 +11091,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="262" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="262" spans="2:12">
       <c r="B262" s="1" t="s">
         <v>3</v>
       </c>
@@ -11080,7 +11123,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="263" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="263" spans="2:12">
       <c r="B263" s="1" t="s">
         <v>3</v>
       </c>
@@ -11112,7 +11155,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="264" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="264" spans="2:12">
       <c r="B264" s="1" t="s">
         <v>3</v>
       </c>
@@ -11144,7 +11187,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="265" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="265" spans="2:12">
       <c r="B265" s="1" t="s">
         <v>3</v>
       </c>
@@ -11176,7 +11219,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="266" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="266" spans="2:12">
       <c r="B266" s="1" t="s">
         <v>3</v>
       </c>
@@ -11208,7 +11251,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="267" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="267" spans="2:12">
       <c r="B267" s="1" t="s">
         <v>3</v>
       </c>
@@ -11240,7 +11283,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="268" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="268" spans="2:12">
       <c r="B268" s="1" t="s">
         <v>3</v>
       </c>
@@ -11272,7 +11315,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="269" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="269" spans="2:12">
       <c r="B269" s="1" t="s">
         <v>3</v>
       </c>
@@ -11304,7 +11347,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="270" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="270" spans="2:12">
       <c r="B270" s="1" t="s">
         <v>3</v>
       </c>
@@ -11336,7 +11379,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="271" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="271" spans="2:12">
       <c r="B271" s="1" t="s">
         <v>3</v>
       </c>
@@ -11368,7 +11411,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="272" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="272" spans="2:12">
       <c r="B272" s="1" t="s">
         <v>3</v>
       </c>
@@ -11400,7 +11443,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="273" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="273" spans="2:12">
       <c r="B273" s="1" t="s">
         <v>3</v>
       </c>
@@ -11432,7 +11475,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="274" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="274" spans="2:12">
       <c r="B274" s="1" t="s">
         <v>3</v>
       </c>
@@ -11464,7 +11507,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="275" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="275" spans="2:12">
       <c r="B275" s="1" t="s">
         <v>3</v>
       </c>
@@ -11496,7 +11539,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="276" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="276" spans="2:12">
       <c r="B276" s="1" t="s">
         <v>3</v>
       </c>
@@ -11528,7 +11571,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="277" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="277" spans="2:12">
       <c r="B277" s="1" t="s">
         <v>3</v>
       </c>
@@ -11560,7 +11603,7 @@
         <v>97.22</v>
       </c>
     </row>
-    <row r="278" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="278" spans="2:12">
       <c r="B278" s="1" t="s">
         <v>3</v>
       </c>
@@ -11592,7 +11635,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="279" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="279" spans="2:12">
       <c r="B279" s="1" t="s">
         <v>3</v>
       </c>
@@ -11624,7 +11667,7 @@
         <v>91.49</v>
       </c>
     </row>
-    <row r="280" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="280" spans="2:12">
       <c r="B280" s="1" t="s">
         <v>3</v>
       </c>
@@ -11656,7 +11699,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="281" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="281" spans="2:12">
       <c r="B281" s="1" t="s">
         <v>3</v>
       </c>
@@ -11688,7 +11731,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="282" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="282" spans="2:12">
       <c r="B282" s="1" t="s">
         <v>3</v>
       </c>
@@ -11720,7 +11763,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="283" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="283" spans="2:12">
       <c r="B283" s="1" t="s">
         <v>3</v>
       </c>
@@ -11752,7 +11795,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="284" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="284" spans="2:12">
       <c r="B284" s="1" t="s">
         <v>3</v>
       </c>
@@ -11784,7 +11827,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="285" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="285" spans="2:12">
       <c r="B285" s="1" t="s">
         <v>3</v>
       </c>
@@ -11816,7 +11859,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="286" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="286" spans="2:12">
       <c r="B286" s="1" t="s">
         <v>3</v>
       </c>
@@ -11848,7 +11891,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="287" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="287" spans="2:12">
       <c r="B287" s="1" t="s">
         <v>3</v>
       </c>
@@ -11880,7 +11923,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="288" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="288" spans="2:12">
       <c r="B288" s="1" t="s">
         <v>3</v>
       </c>
@@ -11912,7 +11955,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="289" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="289" spans="2:12">
       <c r="B289" s="1" t="s">
         <v>3</v>
       </c>
@@ -11944,7 +11987,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="290" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="290" spans="2:12">
       <c r="B290" s="1" t="s">
         <v>3</v>
       </c>
@@ -11976,7 +12019,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="291" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="291" spans="2:12">
       <c r="B291" s="1" t="s">
         <v>3</v>
       </c>
@@ -12008,7 +12051,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="292" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="292" spans="2:12">
       <c r="B292" s="1" t="s">
         <v>3</v>
       </c>
@@ -12040,7 +12083,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="293" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="293" spans="2:12">
       <c r="B293" s="1" t="s">
         <v>3</v>
       </c>
@@ -12072,7 +12115,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="294" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="294" spans="2:12">
       <c r="B294" s="1" t="s">
         <v>3</v>
       </c>
@@ -12104,7 +12147,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="295" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="295" spans="2:12">
       <c r="B295" s="1" t="s">
         <v>3</v>
       </c>
@@ -12136,7 +12179,7 @@
         <v>93.88</v>
       </c>
     </row>
-    <row r="296" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="296" spans="2:12">
       <c r="B296" s="1" t="s">
         <v>3</v>
       </c>
@@ -12168,7 +12211,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="297" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="297" spans="2:12">
       <c r="B297" s="1" t="s">
         <v>3</v>
       </c>
@@ -12200,7 +12243,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="298" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="298" spans="2:12">
       <c r="B298" s="1" t="s">
         <v>3</v>
       </c>
@@ -12232,7 +12275,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="299" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="299" spans="2:12">
       <c r="B299" s="1" t="s">
         <v>3</v>
       </c>
@@ -12264,7 +12307,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="300" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="300" spans="2:12">
       <c r="B300" s="1" t="s">
         <v>3</v>
       </c>
@@ -12296,7 +12339,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="301" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="301" spans="2:12">
       <c r="B301" s="1" t="s">
         <v>3</v>
       </c>
@@ -12328,7 +12371,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="302" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="302" spans="2:12">
       <c r="B302" s="1" t="s">
         <v>3</v>
       </c>
@@ -12360,7 +12403,7 @@
         <v>95.65</v>
       </c>
     </row>
-    <row r="303" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="303" spans="2:12">
       <c r="B303" s="1" t="s">
         <v>3</v>
       </c>
@@ -12392,7 +12435,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="304" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="304" spans="2:12">
       <c r="B304" s="1" t="s">
         <v>3</v>
       </c>
@@ -12424,7 +12467,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="305" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="305" spans="2:12">
       <c r="B305" s="1" t="s">
         <v>3</v>
       </c>
@@ -12456,7 +12499,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="306" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="306" spans="2:12">
       <c r="B306" s="1" t="s">
         <v>3</v>
       </c>
@@ -12488,7 +12531,7 @@
         <v>97.62</v>
       </c>
     </row>
-    <row r="307" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="307" spans="2:12">
       <c r="B307" s="1" t="s">
         <v>3</v>
       </c>
@@ -12520,7 +12563,7 @@
         <v>13.33</v>
       </c>
     </row>
-    <row r="308" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="308" spans="2:12">
       <c r="B308" s="1" t="s">
         <v>3</v>
       </c>
@@ -12552,7 +12595,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="309" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="309" spans="2:12">
       <c r="B309" s="1" t="s">
         <v>3</v>
       </c>
@@ -12584,7 +12627,7 @@
         <v>87.04</v>
       </c>
     </row>
-    <row r="310" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="310" spans="2:12">
       <c r="B310" s="1" t="s">
         <v>3</v>
       </c>
@@ -12616,7 +12659,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="311" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="311" spans="2:12">
       <c r="B311" s="1" t="s">
         <v>3</v>
       </c>
@@ -12648,7 +12691,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="312" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="312" spans="2:12">
       <c r="B312" s="1" t="s">
         <v>3</v>
       </c>
@@ -12680,7 +12723,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="313" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="313" spans="2:12">
       <c r="B313" s="1" t="s">
         <v>3</v>
       </c>
@@ -12712,7 +12755,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="314" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="314" spans="2:12">
       <c r="B314" s="1" t="s">
         <v>3</v>
       </c>
@@ -12744,7 +12787,7 @@
         <v>92.59</v>
       </c>
     </row>
-    <row r="315" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="315" spans="2:12">
       <c r="B315" s="1" t="s">
         <v>3</v>
       </c>
@@ -12776,7 +12819,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="316" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="316" spans="2:12">
       <c r="B316" s="1" t="s">
         <v>3</v>
       </c>
@@ -12808,7 +12851,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="317" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="317" spans="2:12">
       <c r="B317" s="1" t="s">
         <v>3</v>
       </c>
@@ -12840,7 +12883,7 @@
         <v>98.51</v>
       </c>
     </row>
-    <row r="318" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="318" spans="2:12">
       <c r="B318" s="1" t="s">
         <v>3</v>
       </c>
@@ -12872,7 +12915,7 @@
         <v>86.49</v>
       </c>
     </row>
-    <row r="319" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="319" spans="2:12">
       <c r="B319" s="1" t="s">
         <v>3</v>
       </c>
@@ -12904,7 +12947,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="320" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="320" spans="2:12">
       <c r="B320" s="1" t="s">
         <v>3</v>
       </c>
@@ -12936,7 +12979,7 @@
         <v>93.75</v>
       </c>
     </row>
-    <row r="321" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="321" spans="2:12">
       <c r="B321" s="1" t="s">
         <v>3</v>
       </c>
@@ -12968,7 +13011,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="322" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="322" spans="2:12">
       <c r="B322" s="1" t="s">
         <v>3</v>
       </c>
@@ -13000,7 +13043,7 @@
         <v>94.64</v>
       </c>
     </row>
-    <row r="323" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="323" spans="2:12">
       <c r="B323" s="1" t="s">
         <v>3</v>
       </c>
@@ -13032,7 +13075,7 @@
         <v>97.04</v>
       </c>
     </row>
-    <row r="324" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="324" spans="2:12">
       <c r="B324" s="1" t="s">
         <v>3</v>
       </c>
@@ -13064,7 +13107,7 @@
         <v>21.05</v>
       </c>
     </row>
-    <row r="325" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="325" spans="2:12">
       <c r="B325" s="1" t="s">
         <v>3</v>
       </c>
@@ -13096,7 +13139,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="326" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="326" spans="2:12">
       <c r="B326" s="1" t="s">
         <v>3</v>
       </c>
@@ -13128,7 +13171,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="327" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="327" spans="2:12">
       <c r="B327" s="1" t="s">
         <v>3</v>
       </c>
@@ -13160,7 +13203,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="328" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="328" spans="2:12">
       <c r="B328" s="1" t="s">
         <v>3</v>
       </c>
@@ -13192,7 +13235,7 @@
         <v>35.479999999999997</v>
       </c>
     </row>
-    <row r="329" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="329" spans="2:12">
       <c r="B329" s="1" t="s">
         <v>3</v>
       </c>
@@ -13224,7 +13267,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="330" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="330" spans="2:12">
       <c r="B330" s="1" t="s">
         <v>3</v>
       </c>
@@ -13256,7 +13299,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="331" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="331" spans="2:12">
       <c r="B331" s="1" t="s">
         <v>3</v>
       </c>
@@ -13288,7 +13331,7 @@
         <v>86.67</v>
       </c>
     </row>
-    <row r="332" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="332" spans="2:12">
       <c r="B332" s="1" t="s">
         <v>3</v>
       </c>
@@ -13320,7 +13363,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="333" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="333" spans="2:12">
       <c r="B333" s="1" t="s">
         <v>3</v>
       </c>
@@ -13352,7 +13395,7 @@
         <v>94.12</v>
       </c>
     </row>
-    <row r="334" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="334" spans="2:12">
       <c r="B334" s="1" t="s">
         <v>3</v>
       </c>
@@ -13384,7 +13427,7 @@
         <v>8.33</v>
       </c>
     </row>
-    <row r="335" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="335" spans="2:12">
       <c r="B335" s="1" t="s">
         <v>3</v>
       </c>
@@ -13416,7 +13459,7 @@
         <v>11.76</v>
       </c>
     </row>
-    <row r="336" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="336" spans="2:12">
       <c r="B336" s="1" t="s">
         <v>3</v>
       </c>
@@ -13448,7 +13491,7 @@
         <v>52.94</v>
       </c>
     </row>
-    <row r="337" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="337" spans="2:12">
       <c r="B337" s="1" t="s">
         <v>3</v>
       </c>
@@ -13480,7 +13523,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="338" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="338" spans="2:12">
       <c r="B338" s="1" t="s">
         <v>3</v>
       </c>
@@ -13512,7 +13555,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="339" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="339" spans="2:12">
       <c r="B339" s="1" t="s">
         <v>3</v>
       </c>
@@ -13544,7 +13587,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="340" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="340" spans="2:12">
       <c r="B340" s="1" t="s">
         <v>3</v>
       </c>
@@ -13576,7 +13619,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="341" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="341" spans="2:12">
       <c r="B341" s="1" t="s">
         <v>3</v>
       </c>
@@ -13608,7 +13651,7 @@
         <v>22.22</v>
       </c>
     </row>
-    <row r="342" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="342" spans="2:12">
       <c r="B342" s="1" t="s">
         <v>3</v>
       </c>
@@ -13640,7 +13683,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="343" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="343" spans="2:12">
       <c r="B343" s="1" t="s">
         <v>3</v>
       </c>
@@ -13672,7 +13715,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="344" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="344" spans="2:12">
       <c r="B344" s="1" t="s">
         <v>3</v>
       </c>
@@ -13704,7 +13747,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="345" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="345" spans="2:12">
       <c r="B345" s="1" t="s">
         <v>3</v>
       </c>
@@ -13736,7 +13779,7 @@
         <v>91.21</v>
       </c>
     </row>
-    <row r="346" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="346" spans="2:12">
       <c r="B346" s="1" t="s">
         <v>3</v>
       </c>
@@ -13768,7 +13811,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="347" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="347" spans="2:12">
       <c r="B347" s="1" t="s">
         <v>3</v>
       </c>
@@ -13800,7 +13843,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="348" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="348" spans="2:12">
       <c r="B348" s="1" t="s">
         <v>3</v>
       </c>
@@ -13832,7 +13875,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="349" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="349" spans="2:12">
       <c r="B349" s="1" t="s">
         <v>3</v>
       </c>
@@ -13864,7 +13907,7 @@
         <v>64.290000000000006</v>
       </c>
     </row>
-    <row r="350" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="350" spans="2:12">
       <c r="B350" s="1" t="s">
         <v>3</v>
       </c>
@@ -13896,7 +13939,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="351" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="351" spans="2:12">
       <c r="B351" s="1" t="s">
         <v>3</v>
       </c>
@@ -13928,7 +13971,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="352" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="352" spans="2:12">
       <c r="B352" s="1" t="s">
         <v>3</v>
       </c>
@@ -13960,7 +14003,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="353" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="353" spans="2:12">
       <c r="B353" s="1" t="s">
         <v>3</v>
       </c>
@@ -13992,7 +14035,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="354" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="354" spans="2:12">
       <c r="B354" s="1" t="s">
         <v>3</v>
       </c>
@@ -14024,7 +14067,7 @@
         <v>93.33</v>
       </c>
     </row>
-    <row r="355" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="355" spans="2:12">
       <c r="B355" s="1" t="s">
         <v>3</v>
       </c>
@@ -14056,7 +14099,7 @@
         <v>11.11</v>
       </c>
     </row>
-    <row r="356" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="356" spans="2:12">
       <c r="B356" s="1" t="s">
         <v>3</v>
       </c>
@@ -14088,7 +14131,7 @@
         <v>88.24</v>
       </c>
     </row>
-    <row r="357" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="357" spans="2:12">
       <c r="B357" s="1" t="s">
         <v>3</v>
       </c>
@@ -14120,7 +14163,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="358" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="358" spans="2:12">
       <c r="B358" s="1" t="s">
         <v>3</v>
       </c>
@@ -14152,7 +14195,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="359" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="359" spans="2:12">
       <c r="B359" s="1" t="s">
         <v>3</v>
       </c>
@@ -14184,7 +14227,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="360" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="360" spans="2:12">
       <c r="B360" s="1" t="s">
         <v>3</v>
       </c>
@@ -14216,7 +14259,7 @@
         <v>96.77</v>
       </c>
     </row>
-    <row r="361" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="361" spans="2:12">
       <c r="B361" s="1" t="s">
         <v>3</v>
       </c>
@@ -14248,7 +14291,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="362" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="362" spans="2:12">
       <c r="B362" s="1" t="s">
         <v>3</v>
       </c>
@@ -14280,7 +14323,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="363" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="363" spans="2:12">
       <c r="B363" s="1" t="s">
         <v>3</v>
       </c>
@@ -14312,7 +14355,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="364" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="364" spans="2:12">
       <c r="B364" s="1" t="s">
         <v>3</v>
       </c>
@@ -14344,7 +14387,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="365" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="365" spans="2:12">
       <c r="B365" s="1" t="s">
         <v>3</v>
       </c>
@@ -14376,7 +14419,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="366" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="366" spans="2:12">
       <c r="B366" s="1" t="s">
         <v>3</v>
       </c>
@@ -14408,7 +14451,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="367" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="367" spans="2:12">
       <c r="B367" s="1" t="s">
         <v>3</v>
       </c>
@@ -14440,7 +14483,7 @@
         <v>92.86</v>
       </c>
     </row>
-    <row r="368" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="368" spans="2:12">
       <c r="B368" s="1" t="s">
         <v>3</v>
       </c>
@@ -14472,7 +14515,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="369" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="369" spans="2:12">
       <c r="B369" s="1" t="s">
         <v>3</v>
       </c>
@@ -14502,6 +14545,72 @@
       </c>
       <c r="L369" s="1">
         <v>100</v>
+      </c>
+    </row>
+    <row r="370" spans="2:12">
+      <c r="B370" s="14" t="s">
+        <v>3</v>
+      </c>
+      <c r="C370" s="14" t="s">
+        <v>16</v>
+      </c>
+      <c r="D370" s="14" t="s">
+        <v>17</v>
+      </c>
+      <c r="E370" s="14" t="s">
+        <v>757</v>
+      </c>
+      <c r="F370" s="14" t="s">
+        <v>758</v>
+      </c>
+      <c r="G370" s="14" t="s">
+        <v>757</v>
+      </c>
+      <c r="H370" s="14" t="s">
+        <v>757</v>
+      </c>
+      <c r="I370" s="14"/>
+      <c r="J370" s="14" t="s">
+        <v>757</v>
+      </c>
+      <c r="K370" s="14" t="s">
+        <v>757</v>
+      </c>
+      <c r="L370" s="14" t="s">
+        <v>757</v>
+      </c>
+    </row>
+    <row r="371" spans="2:12">
+      <c r="B371" s="14" t="s">
+        <v>3</v>
+      </c>
+      <c r="C371" s="14" t="s">
+        <v>16</v>
+      </c>
+      <c r="D371" s="14" t="s">
+        <v>76</v>
+      </c>
+      <c r="E371" s="14" t="s">
+        <v>757</v>
+      </c>
+      <c r="F371" s="14" t="s">
+        <v>759</v>
+      </c>
+      <c r="G371" s="14" t="s">
+        <v>757</v>
+      </c>
+      <c r="H371" s="14" t="s">
+        <v>757</v>
+      </c>
+      <c r="I371" s="14"/>
+      <c r="J371" s="14" t="s">
+        <v>757</v>
+      </c>
+      <c r="K371" s="14" t="s">
+        <v>757</v>
+      </c>
+      <c r="L371" s="14" t="s">
+        <v>757</v>
       </c>
     </row>
   </sheetData>

--- a/تقييم المكتسبات - العرائش -08-10-2025.xlsx
+++ b/تقييم المكتسبات - العرائش -08-10-2025.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Administrator\OneDrive - OFPPT\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{6DE2081C-DAFB-40AB-B6EB-E5FB1B43FA4A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{BBB398CB-4FF7-4184-88B9-F621AD70BBE8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2563" uniqueCount="760">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2563" uniqueCount="762">
   <si>
     <t>العملية</t>
   </si>
@@ -2312,13 +2312,19 @@
     <t>فرعية أولاد بوزيد</t>
   </si>
   <si>
+    <t>200KK</t>
+  </si>
+  <si>
+    <t>التفتيشية</t>
+  </si>
+  <si>
     <t>.</t>
   </si>
   <si>
+    <t>2000L</t>
+  </si>
+  <si>
     <t>المديرية اللإقليمية</t>
-  </si>
-  <si>
-    <t>التفتيشية</t>
   </si>
 </sst>
 </file>
@@ -14564,20 +14570,20 @@
         <v>758</v>
       </c>
       <c r="G370" s="14" t="s">
-        <v>757</v>
+        <v>759</v>
       </c>
       <c r="H370" s="14" t="s">
-        <v>757</v>
+        <v>759</v>
       </c>
       <c r="I370" s="14"/>
       <c r="J370" s="14" t="s">
-        <v>757</v>
+        <v>759</v>
       </c>
       <c r="K370" s="14" t="s">
-        <v>757</v>
+        <v>759</v>
       </c>
       <c r="L370" s="14" t="s">
-        <v>757</v>
+        <v>759</v>
       </c>
     </row>
     <row r="371" spans="2:12">
@@ -14591,26 +14597,26 @@
         <v>76</v>
       </c>
       <c r="E371" s="14" t="s">
-        <v>757</v>
+        <v>760</v>
       </c>
       <c r="F371" s="14" t="s">
+        <v>761</v>
+      </c>
+      <c r="G371" s="14" t="s">
         <v>759</v>
       </c>
-      <c r="G371" s="14" t="s">
-        <v>757</v>
-      </c>
       <c r="H371" s="14" t="s">
-        <v>757</v>
+        <v>759</v>
       </c>
       <c r="I371" s="14"/>
       <c r="J371" s="14" t="s">
-        <v>757</v>
+        <v>759</v>
       </c>
       <c r="K371" s="14" t="s">
-        <v>757</v>
+        <v>759</v>
       </c>
       <c r="L371" s="14" t="s">
-        <v>757</v>
+        <v>759</v>
       </c>
     </row>
   </sheetData>
